--- a/www/download/COUNTRY.CZE.rpPE.xlsx
+++ b/www/download/COUNTRY.CZE.rpPE.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>República Tcheca</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>26.5322375111802</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>27.1370408253621</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>31.5159153924822</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>32.1646826403424</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>34.518468120635</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>38.431975719047</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>38.008361220193</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>32.5839042490637</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>28.1610815462506</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>25.6476028977032</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>23.9291690489315</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>22.5580866760044</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>20.2224473160373</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.9492103310518</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.9405056976826</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5.148</t>
+          <t>4.61581598182508</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.195</t>
+          <t>2.82481574039148</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5.205</t>
+          <t>3.05346395285095</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5.125</t>
+          <t>2.87938131767309</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.949</t>
+          <t>3.0862561859643</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>3.3276878622429</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.963</t>
+          <t>2.61582304732271</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.991</t>
+          <t>1.9023998645494</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.923</t>
+          <t>1.66064755677908</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>1.28948704057457</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.992</t>
+          <t>1.160271664386</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>5.088</t>
+          <t>1.00094213262058</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>5.224</t>
+          <t>0.845443064300453</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>5.349</t>
+          <t>0.634877514660851</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>5.232</t>
+          <t>0.784649686453427</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.436</t>
+          <t>3.65480783080925</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.447</t>
+          <t>2.1403571854676</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4.419</t>
+          <t>2.27777618057938</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4.301</t>
+          <t>2.03807589184997</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4.103</t>
+          <t>2.20744825152258</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.083</t>
+          <t>2.33527437435799</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.099</t>
+          <t>1.8519337028391</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.085</t>
+          <t>1.28711239129433</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3.981</t>
+          <t>0.899107267685861</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4.011</t>
+          <t>0.818905077953332</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>4.084</t>
+          <t>0.725922622557985</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4.161</t>
+          <t>0.612032971205015</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>4.279</t>
+          <t>0.520727055635874</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>4.336</t>
+          <t>0.307302831022318</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>4.254</t>
+          <t>0.424556986946378</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10385.389</t>
+          <t>1.03286210661699</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10466.783</t>
+          <t>0.397850908284304</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10506.601</t>
+          <t>0.457106860452063</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10374.742</t>
+          <t>0.288707676320212</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>10183.985</t>
+          <t>0.322343793610313</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10157.388</t>
+          <t>0.302891288172512</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>9751.944</t>
+          <t>0.134765977147002</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9700.054</t>
+          <t>-0.107170524087196</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>9578.514</t>
+          <t>-0.429694514678209</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>9651.583</t>
+          <t>-0.255939529286266</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>9808.906</t>
+          <t>-0.2807154240185</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>9974.58</t>
+          <t>-0.307693822490952</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>10175.114</t>
+          <t>-0.34592125245158</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>10460.522</t>
+          <t>-0.428716363400325</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>10103.591</t>
+          <t>-0.371768205337191</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>8581.482</t>
+          <t>50039039188.2153</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8594.152</t>
+          <t>49923027970.0733</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8546.09</t>
+          <t>50965953435.7058</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>8336.71</t>
+          <t>51462464353.6218</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8137.807</t>
+          <t>50804487848.8159</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8094.805</t>
+          <t>50754060656.7064</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7714.352</t>
+          <t>51627598961.1217</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7569.647</t>
+          <t>51431849931.356</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>7358.729</t>
+          <t>46351286905.9642</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7481.786</t>
+          <t>49954613416.0912</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7685.812</t>
+          <t>49439923798.8288</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>7832.395</t>
+          <t>51538766342.7088</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>8030.064</t>
+          <t>49743863223.3319</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>8156.526</t>
+          <t>46329278545.5762</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>8002.884</t>
+          <t>39850702200.5524</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>6270021667.49311</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>9130694732.43547</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>8724997142.35975</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>9576114549.92573</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>9135340345.81533</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>9073370481.51882</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>18.06</t>
+          <t>10230249879.7631</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18.32</t>
+          <t>12442595341.5407</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>13251717830.2902</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>14955746962.3705</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>15923690122.5392</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>16916420948.4119</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>17374014157.6259</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>19673043605.6188</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>18026204807.9823</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>12961280.8137358</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>11735836.4777066</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>12779279.0683863</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>12342949.0390786</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>76.46</t>
+          <t>12798412.3344487</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>76.12</t>
+          <t>13215574.1011791</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>75.98</t>
+          <t>12213066.9678621</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>75.85</t>
+          <t>10347570.524843</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>7589545.61564778</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>75.32</t>
+          <t>6684734.3761475</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>75.49</t>
+          <t>6038449.86197199</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>74.92</t>
+          <t>5339246.64768051</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>74.54</t>
+          <t>4147404.28839189</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>74.27</t>
+          <t>3135364.63050046</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>3453682.55052492</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>83700.031511625</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>83625.3112048552</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>81576.2538703629</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>79746.2194361063</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>79849.5838120782</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>79911.3715536038</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>74314.3875944004</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>74101.4111111053</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>76326.4248832618</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>84782.8618301416</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>92023.6680688226</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>96928.4460754794</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>108457.35954581</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>120518.800158657</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>106993.739435842</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>165100.063911897</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>166627.361543799</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>166428.478600435</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>159434.901773193</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>159345.846173613</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>21.27</t>
+          <t>154872.472297164</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>151965.075322506</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>155431.38632602</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>162400.84363341</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>181819.104170112</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>194972.17476928</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>216123.280475945</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>23.78</t>
+          <t>246566.12261062</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>260925.948664287</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>206745.248074987</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>77.53</t>
+          <t>3.68706845021504</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>77.26</t>
+          <t>2.17085170697937</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>77.11</t>
+          <t>2.32209532182875</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>76.94</t>
+          <t>2.09927885149709</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>76.62</t>
+          <t>2.27798965160473</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>76.25</t>
+          <t>2.42915059423324</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>76.07</t>
+          <t>1.92973338330295</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>75.52</t>
+          <t>1.35570790849498</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>75.53</t>
+          <t>0.971130075522464</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>0.887197516057833</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>0.794765370609245</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>0.674788950503795</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>0.56681263777302</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>73.24</t>
+          <t>0.361664334914378</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>71.31</t>
+          <t>0.495893392044067</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>19360.2057226818</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>21521.4520795566</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>19706.0384506856</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>20615.0327547192</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>19640.284233541</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>18330.6763545838</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>18993.3372687644</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>21957.7937929188</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>25196.3356097143</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>28711.2889260767</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>30459.2137315567</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>32751.7996633133</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>37621.2700643706</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>26.5322375111802</t>
+          <t>1413.5828537035</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>27.1370408253621</t>
+          <t>2053.43165346366</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>31.5159153924822</t>
+          <t>1974.47129804835</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>32.1646826403424</t>
+          <t>2226.56790844529</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>34.518468120635</t>
+          <t>2226.71538343788</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>38.431975719047</t>
+          <t>2222.20955011923</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>38.008361220193</t>
+          <t>2495.76118363111</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>32.5839042490637</t>
+          <t>3045.66351300812</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>28.1610815462506</t>
+          <t>3328.60134485447</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>25.6476028977032</t>
+          <t>3728.6280162846</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>23.9291690489315</t>
+          <t>3898.72665132654</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>22.5580866760044</t>
+          <t>4065.84137662461</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>20.2224473160373</t>
+          <t>4059.86132774367</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>16.9492103310518</t>
+          <t>4537.36080520939</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>18.9405056976826</t>
+          <t>4237.54047914325</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>-3797064313.00833</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>-2793302255.10731</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-3556386003.05525</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>-3428604071.7883</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-3457369866.24436</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>-3618691670.20218</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>-2483243111.97436</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>-1526120004.48513</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-383097148.837775</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>1296940084.37931</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>1797665267.40834</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>2105748739.05134</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>3330431328.11884</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>5102910198.5972</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>4191178926.34923</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>-4056995155.98427</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>-3154246894.73669</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>-3738492300.50734</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>-3596395600.03574</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>-3337037388.45097</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-3502109592.18839</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>-2500639435.67864</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>-1139657990.01065</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>-125511869.685151</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>1888501423.56058</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>2243909529.65829</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>2676820196.38298</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>3799898981.87913</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>5582352347.07314</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>4869534560.43946</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>259930842.975947</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>360944639.629385</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>182106297.452089</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>167791528.247443</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>-120332477.79339</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>-116582078.013791</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>17396323.7042742</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>-386462014.474478</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-257585279.152623</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>-591561339.18127</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>-446244262.249947</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>-571071457.331644</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>-469467653.760295</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-479442148.475941</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-678355634.090232</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>6625.55959535861</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>6511.12726355073</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>6559.38186233156</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>6900.75483006659</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>7299.14998397843</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>7620.29119930213</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>7311.91485643573</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>7174.69362420784</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>6561.10622026717</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>7036.65753063595</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>6997.29958327222</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>6809.42621207204</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>6361.04203591474</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>6178.36238309201</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.458</t>
+          <t>6338.90880126964</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>8310.07636117976</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>8098.76279711267</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>8143.33259898001</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>8583.91745944792</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>8979.81839610982</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>9378.83110276036</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>8997.20536595271</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>8793.91759115727</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>8012.39336925292</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>8562.85020614455</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>8482.91900230173</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>8254.12269850279</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>7666.12171429944</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>7402.11223428797</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>7473.15638730153</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>461.58</t>
+          <t>25501.3563594792</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>282.48</t>
+          <t>27102.9554159455</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>305.35</t>
+          <t>26967.1371907302</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>287.94</t>
+          <t>30641.1681971173</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>308.63</t>
+          <t>30919.5145284852</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>332.77</t>
+          <t>33723.8702890759</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>261.58</t>
+          <t>37945.0674542685</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>190.24</t>
+          <t>43184.0017447542</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>166.06</t>
+          <t>53603.6437525298</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>128.95</t>
+          <t>73695.6695227233</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>116.03</t>
+          <t>85928.973087765</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>100.09</t>
+          <t>103876.178880117</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>84.54</t>
+          <t>133682.141617661</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>63.49</t>
+          <t>160845.920703747</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>78.46</t>
+          <t>121602.409514283</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>365.48</t>
+          <t>10777626647.5664</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>214.04</t>
+          <t>10061583337.1906</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>227.78</t>
+          <t>10900178315.2678</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>203.81</t>
+          <t>11732849599.7215</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>220.74</t>
+          <t>12426645952.8087</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>233.53</t>
+          <t>13450174269.6471</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>185.19</t>
+          <t>13932135737.7188</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>128.71</t>
+          <t>13946512825.6012</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>13254782380.6216</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>15946791077.1709</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>72.59</t>
+          <t>16825576819.4867</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>17829268650.8534</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>52.07</t>
+          <t>18383416507.6492</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>30.73</t>
+          <t>17375540945.8044</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>42.46</t>
+          <t>14237448097.792</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>103.29</t>
+          <t>27596.0165001215</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>39.79</t>
+          <t>30603.8070708168</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>45.71</t>
+          <t>29732.2202731308</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>28.87</t>
+          <t>31512.8098103974</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>31669.8019193873</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>35362.2127479322</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>13.48</t>
+          <t>39436.9402112373</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-10.72</t>
+          <t>44180.7672190162</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-42.97</t>
+          <t>54904.7753543763</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-25.59</t>
+          <t>72308.1610802052</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-28.07</t>
+          <t>81433.6111258701</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-30.77</t>
+          <t>98543.6789830382</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-34.59</t>
+          <t>123846.643864586</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-42.87</t>
+          <t>149210.147984136</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-37.18</t>
+          <t>110242.021836695</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>42782.176</t>
+          <t>7788070235.52804</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>42074.401</t>
+          <t>8571546041.56361</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>42384.89</t>
+          <t>8305313251.44259</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>43988.543</t>
+          <t>8640963712.9077</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>44444.264</t>
+          <t>9276763403.99196</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>46335.768</t>
+          <t>10541062177.2162</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>44652.797</t>
+          <t>12132856860.0425</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>43888.218</t>
+          <t>12869964743.9692</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>39448.586</t>
+          <t>13382708508.6369</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>42303.657</t>
+          <t>16715976255.529</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>42343.491</t>
+          <t>17062043938.8394</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>41999.783</t>
+          <t>18270599435.6876</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>40046.593</t>
+          <t>19135268355.9882</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>39592.828</t>
+          <t>19827134852.4474</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>39098.812</t>
+          <t>15530534409.9498</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>29388.021</t>
+          <t>-2094.66014064229</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>28952.079</t>
+          <t>-3500.85165487135</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>28985.272</t>
+          <t>-2765.08308240057</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>29679.049</t>
+          <t>-871.641613280143</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>29945.551</t>
+          <t>-750.287390902122</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>31113.954</t>
+          <t>-1638.34245885631</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>29971.905</t>
+          <t>-1491.87275696879</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>29311.12</t>
+          <t>-996.765474261954</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>26120.86</t>
+          <t>-1301.13160184649</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>28224.449</t>
+          <t>1387.50844251806</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>28579.288</t>
+          <t>4495.36196189493</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>28331.435</t>
+          <t>5332.49989707869</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>27221.825</t>
+          <t>9835.49775307494</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>26788.082</t>
+          <t>11635.7727196113</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>26965.281</t>
+          <t>11360.3876775878</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>50039.039</t>
+          <t>2989556412.03839</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>49923.028</t>
+          <t>1490037295.62696</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>50965.953</t>
+          <t>2594865063.82518</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>51462.464</t>
+          <t>3091885886.81377</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>50804.488</t>
+          <t>3149882548.81673</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>50754.061</t>
+          <t>2909112092.43088</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>51627.599</t>
+          <t>1799278877.67629</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>51431.85</t>
+          <t>1076548081.63198</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>46351.287</t>
+          <t>-127926128.015359</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>49954.613</t>
+          <t>-769185178.358026</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>49439.924</t>
+          <t>-236467119.352749</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>51538.766</t>
+          <t>-441330784.834254</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>49743.863</t>
+          <t>-751851848.338983</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>46329.279</t>
+          <t>-2451593906.64295</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>39850.702</t>
+          <t>-1293086312.15787</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>27878.01033</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>32918.62252</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>29808.81218</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>31349.72661</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>29897.70559</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>27530.30469</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>30235.26834</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>36643.67487</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>43725.62879</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>54007.07428</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>59661.11896</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>69554.79096</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>84239.06212</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>103702.84821</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>89365.7284</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>25368.065</t>
+          <t>0.0360464818253515</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>25054.881</t>
+          <t>0.00690276113506562</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>24981.371</t>
+          <t>0.00689411741140073</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25740.518</t>
+          <t>0.0146545057878615</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>25458.569</t>
+          <t>0.0166149122900559</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>26188.17</t>
+          <t>0.0172282398678545</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>25247.073</t>
+          <t>0.019940059306721</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>24519.968</t>
+          <t>0.021263592095755</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>21784.542</t>
+          <t>0.0221380796376636</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>23294.005</t>
+          <t>0.0297937853320951</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>23334.833</t>
+          <t>0.0363481868125521</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>23114.458</t>
+          <t>0.0458704902145603</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>21880.898</t>
+          <t>0.0539254635536336</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>21398.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>20623.331</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>18220.6268033519</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>27187.0100592577</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>25267.2653929607</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>26126.5752365978</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>25163.5732089882</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>23884.7725715342</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>26170.0574150603</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>32666.5579290532</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>40090.0440019927</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>46874.1269933221</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>53686.4442984798</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>61450.9121663255</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>74981.2805796816</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>95746.3264610447</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>83007.720834956</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>6270.022</t>
+          <t>21775.8771342148</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>9130.695</t>
+          <t>32631.1792220981</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>8724.997</t>
+          <t>30678.5639491407</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>9576.115</t>
+          <t>32059.7484407347</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>9135.34</t>
+          <t>30953.1831688823</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>9073.37</t>
+          <t>29538.7840449964</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10230.25</t>
+          <t>32567.5223859693</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>12442.595</t>
+          <t>41127.6238857033</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>13251.718</t>
+          <t>51135.9488229703</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>14955.747</t>
+          <t>59309.022845279</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>15923.69</t>
+          <t>67189.3686554274</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>16916.421</t>
+          <t>76949.7458276835</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>17374.014</t>
+          <t>93596.0911283756</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>19673.044</t>
+          <t>119867.694073496</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>18026.205</t>
+          <t>103968.870192087</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>368.71</t>
+          <t>245498.944834045</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>217.09</t>
+          <t>262404.984455268</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>232.21</t>
+          <t>246863.545920945</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>209.93</t>
+          <t>251535.982032188</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>227.8</t>
+          <t>232354.061230121</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>242.92</t>
+          <t>217074.06555197</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>192.97</t>
+          <t>227769.80376059</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>135.57</t>
+          <t>266309.526907654</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>97.11</t>
+          <t>310306.857222978</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>88.72</t>
+          <t>356175.937376202</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>79.48</t>
+          <t>389305.140198336</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>67.48</t>
+          <t>418461.297431486</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>56.68</t>
+          <t>480946.802273826</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>12.961</t>
+          <t>21775.8771342148</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>11.736</t>
+          <t>30143.056266772</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12.779</t>
+          <t>30562.7547582315</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>12.343</t>
+          <t>29723.8298489291</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>12.798</t>
+          <t>30221.9533004683</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>13.216</t>
+          <t>31252.5152808888</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>12.213</t>
+          <t>32282.2501246377</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>10.348</t>
+          <t>33807.7953334713</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>35840.1826172663</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>6.685</t>
+          <t>37028.468444557</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>6.038</t>
+          <t>39734.8868380869</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>5.339</t>
+          <t>42832.1023575882</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>4.147</t>
+          <t>45701.8534384225</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>3.135</t>
+          <t>49687.8598339644</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>3.454</t>
+          <t>45845.1677299452</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>18220.6268033519</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>25017.9801352588</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>24997.9531794996</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>23988.5354534885</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>24331.4543688855</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>25213.3004591456</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>25830.5575065606</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>26885.4825903074</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>28019.7303953848</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>29184.5585467041</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>31791.5898054579</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>34430.0084207251</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>37081.9917019284</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>40513.2280366051</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>37041.6996023775</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>28209.5789757852</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>23332.7710079019</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>21407.9447208593</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>24301.1682592653</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>23500.8265811177</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>22070.4804250036</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>23535.0806640307</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>27620.4909442967</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>32065.9335270297</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>39323.118344721</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>44609.7496945726</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>51946.8245123165</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>63556.5493216244</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>77584.1123065039</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>67265.4924279131</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>29388020739.8717</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>28952078978.2506</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>28985272189.6025</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>29679049304.0984</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>29945551117.4698</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>31113953778.3986</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>29971904592.2729</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>29311120248.2703</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>26120859567.6224</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>28224448518.1751</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>28579287604.2458</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>28331434886.4712</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>27221824951.0157</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>26788081836.9865</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>26965280655.8938</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>42782176114.8401</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>42074400928.099</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>42384889824.4619</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>43988542538.4646</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>44444264178.7861</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>46335768046.4367</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>44652797334.6248</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>43888217836.3154</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>39448586084.2748</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>42303656835.7806</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>42343491184.4314</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>41999782691.6997</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>40046593256.026</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>39592827835.9758</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>39098812367.9339</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>25368065024.4935</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>25054881212.8234</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>24981370923.8904</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>25740518101.2677</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>25458568942.5114</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>26188169781.4576</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>25247073326.7017</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>24519968238.4232</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>21784542118.8611</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>23294004809.7037</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>23334832995.5037</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>23114458207.5785</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>21880897512.1471</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>21398979638.1386</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>20623330825.1649</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>5148229</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>5195164</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>5204858</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>5124530</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4949350</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4940463</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4962963</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4990747</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4923446</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4940371</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4991618</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>5088340</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>5223840</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>5348855.37841137</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5231900.73131227</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>4435553</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>4446554</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>4418903</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>4300841</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>4102608</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>4083040</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4099050</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>4085348</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3981167</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>4011059</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>4084331</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>4160620</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>4279460</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>4335790</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>4253931</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>10385389000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>10466783000</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>10506601000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>10374742000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>10183985000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>10157388000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>9751944000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>9700054000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>9578514000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>9651583000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>9808906000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>9974580000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>10175114000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>10460522320.2866</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>10103590571.8892</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>8581482000</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>8594152000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>8546090000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>8336710000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>8137807000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>8094805000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>7714352000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>7569647000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>7358729000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>7481786000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>7685812000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>7832395000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>8030064000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>8156526000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>8002883825.01644</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.166573778616233</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.166573778616233</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.166573778616233</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.166573778616233</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.169692810054207</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.174571254618226</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.180603645253425</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.183167233522844</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.164338498629227</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.196551407834206</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.199010445363947</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.204605442127207</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.204820376511823</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.207445680303656</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.22328919934111</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.766760438555195</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.766760438555195</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.766760438555195</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.766760438555195</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.764606255087522</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.761221530850925</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.759783404645724</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.758548259103415</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.755796073865582</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.753244363573396</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.754922311106197</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.749235944721564</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.745383539411571</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.742689920171966</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.730952614362941</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.0666657828285725</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.0666657828285725</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.0666657828285725</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.0666657828285725</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.0657009348582706</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.0642072145308483</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.0596129501008513</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.0582845073737414</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.0798654275051914</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0502042285923985</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0460672435298555</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0461586131512284</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0497960840766058</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0498643995243779</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0457581862959489</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.195738153131984</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.197941792217399</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.199507028388376</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.202529044072281</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.206853922159065</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.212716340419057</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.216030604087627</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.222782891550221</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.222030350730464</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.233551011836644</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.234749422729202</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.241074563390058</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.237762534062421</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.246858486399837</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.268177610740323</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.775258934872724</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.77256008446739</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.771145438454611</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.769413961659692</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.766237531325325</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.762495452665945</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.760712345028576</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.755223535194773</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.755258973242011</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.746797113968613</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.746976424801815</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.740170647870372</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.741844249607334</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.732422152224287</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.713063875678945</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.0290029119952918</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.0294981233152117</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0293475331570133</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.0280569942680268</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.0269085465156093</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.0247882069149978</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0232570508837974</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0219935732550058</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.022710676027525</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0196518741947433</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.018274152468983</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0187547887395697</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0203932163302459</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0207193613758765</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0187585135807322</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>131930.33656</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>145588.42367</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>138889.0318</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>148099.64303</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>141552.28303</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>139960.6931</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>154545.02045</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>185157.89271</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>226745.6239</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>275233.32295</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>310792.53065</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>368770.01749</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>456657.19042</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>564946.54779</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>458086.21635</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>49985.45611</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>55963.95023</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>52086.50867</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>56360.9167</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>54454.00975</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>51609.26447</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>56102.60305</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>68748.11483</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>83201.88235</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>98632.14119</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>111799.11835</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>128896.57034</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>157152.64045</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>197451.80638</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>171234.36262</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>6513636.35600347</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>6732155.90104509</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>6916439.49357942</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>7098294.2932243</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>7283933.21595949</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>7494372.74102545</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>7750162.13301742</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>7975477.2427386</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>8180646.87159439</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>8397388.0706155</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>8599857.0472584</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>8854511.26223221</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>9152706.06043163</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
